--- a/Lab_4/data/partB/param_optimization_process/v200_k20_s100_results.xlsx
+++ b/Lab_4/data/partB/param_optimization_process/v200_k20_s100_results.xlsx
@@ -518,13 +518,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -533,28 +533,28 @@
         <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
         <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
+        <v>14</v>
+      </c>
+      <c r="N2" t="n">
         <v>2</v>
-      </c>
-      <c r="M2" t="n">
-        <v>10</v>
-      </c>
-      <c r="N2" t="n">
-        <v>4</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -570,16 +570,16 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>72</v>
+      </c>
+      <c r="D3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" t="n">
-        <v>47</v>
-      </c>
-      <c r="D3" t="n">
-        <v>3</v>
-      </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -588,19 +588,19 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -609,7 +609,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -625,10 +625,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -646,16 +646,16 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" t="n">
         <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -674,22 +674,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
@@ -698,22 +698,22 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -729,46 +729,46 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>29</v>
+      </c>
+      <c r="G6" t="n">
+        <v>8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>11</v>
+      </c>
+      <c r="J6" t="n">
         <v>3</v>
       </c>
-      <c r="F6" t="n">
-        <v>27</v>
-      </c>
-      <c r="G6" t="n">
-        <v>11</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4</v>
-      </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>17</v>
+      </c>
+      <c r="N6" t="n">
+        <v>7</v>
+      </c>
+      <c r="O6" t="n">
         <v>1</v>
       </c>
-      <c r="M6" t="n">
-        <v>16</v>
-      </c>
-      <c r="N6" t="n">
-        <v>14</v>
-      </c>
-      <c r="O6" t="n">
-        <v>4</v>
-      </c>
       <c r="P6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -787,40 +787,40 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>11</v>
+      </c>
+      <c r="G7" t="n">
+        <v>52</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
         <v>4</v>
       </c>
-      <c r="F7" t="n">
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
         <v>8</v>
-      </c>
-      <c r="G7" t="n">
-        <v>48</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I7" t="n">
-        <v>6</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>7</v>
-      </c>
-      <c r="N7" t="n">
-        <v>7</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -839,40 +839,40 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H8" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I8" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -882,49 +882,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -934,13 +934,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -958,7 +958,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -973,7 +973,7 @@
         <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -998,37 +998,37 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N11" t="n">
         <v>2</v>
       </c>
       <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
         <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1041,16 +1041,16 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1062,25 +1062,25 @@
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="M12" t="n">
         <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1090,49 +1090,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="N13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1142,31 +1142,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
         <v>1</v>
       </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1175,16 +1175,16 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -1200,16 +1200,16 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" t="n">
         <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1218,13 +1218,13 @@
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>1</v>
@@ -1233,7 +1233,7 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1246,22 +1246,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G16" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
@@ -1270,25 +1270,25 @@
         <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6112,7 +6112,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -7778,7 +7778,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8543,7 +8543,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8713,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9121,7 +9121,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -9580,7 +9580,7 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -10141,7 +10141,7 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -10175,7 +10175,7 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10464,7 +10464,7 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -10583,7 +10583,7 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10906,7 +10906,7 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10923,7 +10923,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11059,7 +11059,7 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11127,7 +11127,7 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11212,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11246,7 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11331,7 +11331,7 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -11365,7 +11365,7 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -11416,7 +11416,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11756,7 +11756,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11841,7 +11841,7 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11909,7 +11909,7 @@
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11960,7 +11960,7 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12045,7 +12045,7 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12266,7 +12266,7 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12334,7 +12334,7 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12368,7 +12368,7 @@
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12385,7 +12385,7 @@
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12436,7 +12436,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12487,7 +12487,7 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12504,7 +12504,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12555,7 +12555,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12657,7 +12657,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12708,7 +12708,7 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12827,7 +12827,7 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12929,7 +12929,7 @@
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12963,7 +12963,7 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13031,7 +13031,7 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13048,7 +13048,7 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13082,7 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13201,7 +13201,7 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13218,7 +13218,7 @@
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13235,7 +13235,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13303,7 +13303,7 @@
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13354,7 +13354,7 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13439,7 +13439,7 @@
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13456,7 +13456,7 @@
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13609,7 +13609,7 @@
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -13626,7 +13626,7 @@
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13677,7 +13677,7 @@
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13762,7 +13762,7 @@
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13983,7 +13983,7 @@
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14000,7 +14000,7 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14187,7 +14187,7 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14221,7 +14221,7 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14238,7 +14238,7 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -14323,7 +14323,7 @@
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14374,7 +14374,7 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -14425,7 +14425,7 @@
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14459,7 +14459,7 @@
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14595,7 +14595,7 @@
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14646,7 +14646,7 @@
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14748,7 +14748,7 @@
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14782,7 +14782,7 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -14816,7 +14816,7 @@
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14884,7 +14884,7 @@
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14901,7 +14901,7 @@
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14935,7 +14935,7 @@
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15020,7 +15020,7 @@
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15037,7 +15037,7 @@
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15088,7 +15088,7 @@
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15122,7 +15122,7 @@
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -15207,7 +15207,7 @@
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15241,7 +15241,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -15258,7 +15258,7 @@
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15343,7 +15343,7 @@
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -15377,7 +15377,7 @@
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15513,7 +15513,7 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15615,7 +15615,7 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15802,7 +15802,7 @@
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15819,7 +15819,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15853,7 +15853,7 @@
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15989,7 +15989,7 @@
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16057,7 +16057,7 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16261,7 +16261,7 @@
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="C893" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16754,7 +16754,7 @@
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16771,7 +16771,7 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16856,7 +16856,7 @@
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -16924,7 +16924,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17026,7 +17026,7 @@
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17077,7 +17077,7 @@
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17128,7 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17298,7 +17298,7 @@
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -17315,7 +17315,7 @@
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17434,7 +17434,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -17451,7 +17451,7 @@
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17485,7 +17485,7 @@
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17519,7 +17519,7 @@
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17536,7 +17536,7 @@
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="C956" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="C960" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17638,7 +17638,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17672,7 +17672,7 @@
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17689,7 +17689,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17791,7 +17791,7 @@
       </c>
       <c r="C970" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17859,7 +17859,7 @@
       </c>
       <c r="C974" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17876,7 +17876,7 @@
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17893,7 +17893,7 @@
       </c>
       <c r="C976" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17927,7 +17927,7 @@
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17944,7 +17944,7 @@
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17961,7 +17961,7 @@
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -17978,7 +17978,7 @@
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17995,7 +17995,7 @@
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="C983" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18063,7 +18063,7 @@
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -18080,7 +18080,7 @@
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18131,7 +18131,7 @@
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18148,7 +18148,7 @@
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18301,7 +18301,7 @@
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -18454,7 +18454,7 @@
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18505,7 +18505,7 @@
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18573,7 +18573,7 @@
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18624,7 +18624,7 @@
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18641,7 +18641,7 @@
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18658,7 +18658,7 @@
       </c>
       <c r="C1021" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18675,7 +18675,7 @@
       </c>
       <c r="C1022" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18692,7 +18692,7 @@
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18743,7 +18743,7 @@
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18811,7 +18811,7 @@
       </c>
       <c r="C1030" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18862,7 +18862,7 @@
       </c>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18896,7 +18896,7 @@
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18913,7 +18913,7 @@
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18947,7 +18947,7 @@
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19032,7 +19032,7 @@
       </c>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19049,7 +19049,7 @@
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19083,7 +19083,7 @@
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19117,7 +19117,7 @@
       </c>
       <c r="C1048" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19134,7 +19134,7 @@
       </c>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19185,7 +19185,7 @@
       </c>
       <c r="C1052" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19270,7 +19270,7 @@
       </c>
       <c r="C1057" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -19304,7 +19304,7 @@
       </c>
       <c r="C1059" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19355,7 +19355,7 @@
       </c>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19389,7 +19389,7 @@
       </c>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19440,7 +19440,7 @@
       </c>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19474,7 +19474,7 @@
       </c>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19491,7 +19491,7 @@
       </c>
       <c r="C1070" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19627,7 +19627,7 @@
       </c>
       <c r="C1078" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="C1082" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19729,7 +19729,7 @@
       </c>
       <c r="C1084" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19746,7 +19746,7 @@
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="C1097" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19967,7 +19967,7 @@
       </c>
       <c r="C1098" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -19984,7 +19984,7 @@
       </c>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -20137,7 +20137,7 @@
       </c>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -20205,7 +20205,7 @@
       </c>
       <c r="C1112" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="C1116" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20358,7 +20358,7 @@
       </c>
       <c r="C1121" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20409,7 +20409,7 @@
       </c>
       <c r="C1124" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20426,7 +20426,7 @@
       </c>
       <c r="C1125" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20562,7 +20562,7 @@
       </c>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -20579,7 +20579,7 @@
       </c>
       <c r="C1134" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20630,7 +20630,7 @@
       </c>
       <c r="C1137" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -20715,7 +20715,7 @@
       </c>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20732,7 +20732,7 @@
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20868,7 +20868,7 @@
       </c>
       <c r="C1151" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20953,7 +20953,7 @@
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20987,7 +20987,7 @@
       </c>
       <c r="C1158" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21055,7 +21055,7 @@
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -21123,7 +21123,7 @@
       </c>
       <c r="C1166" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -21140,7 +21140,7 @@
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21225,7 +21225,7 @@
       </c>
       <c r="C1172" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21293,7 +21293,7 @@
       </c>
       <c r="C1176" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21310,7 +21310,7 @@
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21446,7 +21446,7 @@
       </c>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="C1186" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21650,7 +21650,7 @@
       </c>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21684,7 +21684,7 @@
       </c>
       <c r="C1199" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21701,7 +21701,7 @@
       </c>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21786,7 +21786,7 @@
       </c>
       <c r="C1205" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -21803,7 +21803,7 @@
       </c>
       <c r="C1206" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22126,7 +22126,7 @@
       </c>
       <c r="C1225" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22143,7 +22143,7 @@
       </c>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="C1227" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="C1228" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22194,7 +22194,7 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -22245,7 +22245,7 @@
       </c>
       <c r="C1232" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22262,7 +22262,7 @@
       </c>
       <c r="C1233" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22279,7 +22279,7 @@
       </c>
       <c r="C1234" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22296,7 +22296,7 @@
       </c>
       <c r="C1235" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22330,7 +22330,7 @@
       </c>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22381,7 +22381,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -22449,7 +22449,7 @@
       </c>
       <c r="C1244" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22483,7 +22483,7 @@
       </c>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22500,7 +22500,7 @@
       </c>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22517,7 +22517,7 @@
       </c>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22534,7 +22534,7 @@
       </c>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22636,7 +22636,7 @@
       </c>
       <c r="C1255" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -22670,7 +22670,7 @@
       </c>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -22704,7 +22704,7 @@
       </c>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22772,7 +22772,7 @@
       </c>
       <c r="C1263" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22789,7 +22789,7 @@
       </c>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -22840,7 +22840,7 @@
       </c>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22857,7 +22857,7 @@
       </c>
       <c r="C1268" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22891,7 +22891,7 @@
       </c>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22993,7 +22993,7 @@
       </c>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23027,7 +23027,7 @@
       </c>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23180,7 +23180,7 @@
       </c>
       <c r="C1287" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23197,7 +23197,7 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23299,7 +23299,7 @@
       </c>
       <c r="C1294" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23316,7 +23316,7 @@
       </c>
       <c r="C1295" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23350,7 +23350,7 @@
       </c>
       <c r="C1297" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23401,7 @@
       </c>
       <c r="C1300" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23469,7 +23469,7 @@
       </c>
       <c r="C1304" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23758,7 +23758,7 @@
       </c>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -24302,7 +24302,7 @@
       </c>
       <c r="C1353" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25016,7 +25016,7 @@
       </c>
       <c r="C1395" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="C1397" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -25118,7 +25118,7 @@
       </c>
       <c r="C1401" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -25220,7 +25220,7 @@
       </c>
       <c r="C1407" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25271,7 +25271,7 @@
       </c>
       <c r="C1410" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25339,7 +25339,7 @@
       </c>
       <c r="C1414" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25492,7 +25492,7 @@
       </c>
       <c r="C1423" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25509,7 +25509,7 @@
       </c>
       <c r="C1424" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25594,7 +25594,7 @@
       </c>
       <c r="C1429" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -25628,7 +25628,7 @@
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25645,7 +25645,7 @@
       </c>
       <c r="C1432" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25662,7 +25662,7 @@
       </c>
       <c r="C1433" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -25696,7 +25696,7 @@
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25747,7 +25747,7 @@
       </c>
       <c r="C1438" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -25764,7 +25764,7 @@
       </c>
       <c r="C1439" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25781,7 +25781,7 @@
       </c>
       <c r="C1440" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25866,7 +25866,7 @@
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C1448" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -25951,7 +25951,7 @@
       </c>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -26019,7 +26019,7 @@
       </c>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26053,7 +26053,7 @@
       </c>
       <c r="C1456" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26138,7 +26138,7 @@
       </c>
       <c r="C1461" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26172,7 +26172,7 @@
       </c>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26308,7 +26308,7 @@
       </c>
       <c r="C1471" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26325,7 +26325,7 @@
       </c>
       <c r="C1472" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26393,7 +26393,7 @@
       </c>
       <c r="C1476" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26410,7 +26410,7 @@
       </c>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26444,7 +26444,7 @@
       </c>
       <c r="C1479" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26478,7 +26478,7 @@
       </c>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="C1483" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -26563,7 +26563,7 @@
       </c>
       <c r="C1486" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26580,7 +26580,7 @@
       </c>
       <c r="C1487" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="C1488" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26631,7 +26631,7 @@
       </c>
       <c r="C1490" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26733,7 +26733,7 @@
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26750,7 +26750,7 @@
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26767,7 +26767,7 @@
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26801,7 +26801,7 @@
       </c>
       <c r="C1500" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
